--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.659.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.659.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
   <si>
     <t>Property</t>
   </si>
@@ -74,19 +74,7 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>ANS (https://esante.gouv.fr)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -385,7 +373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -477,43 +465,27 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>9</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -532,42 +504,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -586,34 +558,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -632,34 +604,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -678,50 +650,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -740,34 +712,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -786,138 +758,138 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.659.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.659.xlsx
@@ -10,15 +10,12 @@
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
-    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
-    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="74">
   <si>
     <t>Property</t>
   </si>
@@ -68,13 +65,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T01:00:00+02:00</t>
+    <t>2023-04-28T00:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+    <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -95,10 +92,142 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>N18.9</t>
+  </si>
+  <si>
+    <t>Maladie rénale chronique, sans précision</t>
+  </si>
+  <si>
+    <t>I50.9</t>
+  </si>
+  <si>
+    <t>Insuffisance cardiaque, sans précision</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/icd10</t>
+  </si>
+  <si>
+    <t>MED-1105</t>
+  </si>
+  <si>
+    <t>Hypersensibilité au PDC iodé</t>
+  </si>
+  <si>
+    <t>MED-1106</t>
+  </si>
+  <si>
+    <t>Hyperthyroidie non traitée</t>
+  </si>
+  <si>
+    <t>MED-1107</t>
+  </si>
+  <si>
+    <t>Antécédents chirurgicaux digestifs récents contre-indiquant l’usage de produit baryté et nécessitant l’usage d’un produit hydrosoluble</t>
+  </si>
+  <si>
+    <t>MED-1108</t>
+  </si>
+  <si>
+    <t>Hypersensibilité au PDC ultrasonore</t>
+  </si>
+  <si>
+    <t>MED-1109</t>
+  </si>
+  <si>
+    <t>Patient claustrophobe</t>
+  </si>
+  <si>
+    <t>MED-1110</t>
+  </si>
+  <si>
+    <t>Patient porteur de corps étranger ferromagnétique (œil ou autre)</t>
+  </si>
+  <si>
+    <t>MED-1111</t>
+  </si>
+  <si>
+    <t>Patient porteur de clips métalliques ou coils intracrâniens</t>
+  </si>
+  <si>
+    <t>MED-1112</t>
+  </si>
+  <si>
+    <t>Patient porteur d’un implant cochléaire</t>
+  </si>
+  <si>
+    <t>MED-1113</t>
+  </si>
+  <si>
+    <t>Patient porteur d’un neurostimulateur</t>
+  </si>
+  <si>
+    <t>MED-1114</t>
+  </si>
+  <si>
+    <t>Patient porteur d’une sonde de dérivation du LCS</t>
+  </si>
+  <si>
+    <t>MED-1115</t>
+  </si>
+  <si>
+    <t>Patient porteur d’un capteur implanté</t>
+  </si>
+  <si>
+    <t>MED-1116</t>
+  </si>
+  <si>
+    <t>Patient porteur d’une pompe implantée</t>
+  </si>
+  <si>
+    <t>MED-1117</t>
+  </si>
+  <si>
+    <t>Patient porteur de Pacemaker</t>
+  </si>
+  <si>
+    <t>MED-1118</t>
+  </si>
+  <si>
+    <t>Patient porteur d’une valve cardiaque mécanique</t>
+  </si>
+  <si>
+    <t>MED-1119</t>
+  </si>
+  <si>
+    <t>Patient porteur d’un matériel d'orthodontie</t>
+  </si>
+  <si>
+    <t>MED-1120</t>
+  </si>
+  <si>
+    <t>Patient porteur d’un stent ou un filtre cave</t>
+  </si>
+  <si>
+    <t>MED-1122</t>
+  </si>
+  <si>
+    <t>Hypersensibilité au produit de contraste gadoliné</t>
+  </si>
+  <si>
+    <t>GEN-092.01.20</t>
+  </si>
+  <si>
+    <t>Autre contre-indication connue</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
+  </si>
+  <si>
     <t>77386006</t>
   </si>
   <si>
-    <t>Enceinte</t>
+    <t>enceinte</t>
   </si>
   <si>
     <t>1260078007</t>
@@ -107,139 +236,7 @@
     <t>Allaitement</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>urn:oid:2.16.840.1.113883.6.96</t>
-  </si>
-  <si>
-    <t>MED-1105</t>
-  </si>
-  <si>
-    <t>Hypersensibilité au PDC iodé</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
-  </si>
-  <si>
-    <t>N18.9</t>
-  </si>
-  <si>
-    <t>Maladie rénale chronique, sans précision</t>
-  </si>
-  <si>
-    <t>urn:oid:2.16.840.1.113883.6.3</t>
-  </si>
-  <si>
-    <t>MED-1106</t>
-  </si>
-  <si>
-    <t>Hyperthyroidie non traitée</t>
-  </si>
-  <si>
-    <t>MED-1107</t>
-  </si>
-  <si>
-    <t>Antécédents chirurgicaux digestifs récents contre-indiquant l’usage de produit baryté et nécessitant l’usage d’un produit hydrosoluble</t>
-  </si>
-  <si>
-    <t>MED-1108</t>
-  </si>
-  <si>
-    <t>Hypersensibilité au PDC ultrasonore</t>
-  </si>
-  <si>
-    <t>I50.9</t>
-  </si>
-  <si>
-    <t>Insuffisance cardiaque, sans précision</t>
-  </si>
-  <si>
-    <t>MED-1109</t>
-  </si>
-  <si>
-    <t>Patient claustrophobe</t>
-  </si>
-  <si>
-    <t>MED-1110</t>
-  </si>
-  <si>
-    <t>Patient porteur de corps étranger ferromagnétique (œil ou autre)</t>
-  </si>
-  <si>
-    <t>MED-1111</t>
-  </si>
-  <si>
-    <t>Patient porteur de clips métalliques ou coils intracrâniens</t>
-  </si>
-  <si>
-    <t>MED-1112</t>
-  </si>
-  <si>
-    <t>Patient porteur d’un implant cochléaire</t>
-  </si>
-  <si>
-    <t>MED-1113</t>
-  </si>
-  <si>
-    <t>Patient porteur d’un neurostimulateur</t>
-  </si>
-  <si>
-    <t>MED-1114</t>
-  </si>
-  <si>
-    <t>Patient porteur d’une sonde de dérivation du LCS</t>
-  </si>
-  <si>
-    <t>MED-1115</t>
-  </si>
-  <si>
-    <t>Patient porteur d’un capteur implanté</t>
-  </si>
-  <si>
-    <t>MED-1116</t>
-  </si>
-  <si>
-    <t>Patient porteur d’une pompe implantée</t>
-  </si>
-  <si>
-    <t>MED-1117</t>
-  </si>
-  <si>
-    <t>Patient porteur de Pacemaker</t>
-  </si>
-  <si>
-    <t>MED-1118</t>
-  </si>
-  <si>
-    <t>Patient porteur d’une valve cardiaque mécanique</t>
-  </si>
-  <si>
-    <t>MED-1119</t>
-  </si>
-  <si>
-    <t>Patient porteur d’un matériel d'orthodontie</t>
-  </si>
-  <si>
-    <t>MED-1120</t>
-  </si>
-  <si>
-    <t>Patient porteur d’un stent ou un filtre cave</t>
-  </si>
-  <si>
-    <t>MED-1122</t>
-  </si>
-  <si>
-    <t>Hypersensibilité au produit de contraste gadoliné</t>
-  </si>
-  <si>
-    <t>GEN-092.01.20</t>
-  </si>
-  <si>
-    <t>Autre contre-indication connue</t>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -549,7 +546,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -574,18 +571,154 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
+      <c r="B21" t="s" s="2">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -595,7 +728,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -612,284 +745,34 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>36</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>29</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="B15" t="s" s="2">
         <v>73</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.659.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.659.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -370,7 +376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -462,27 +468,35 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>23</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -501,42 +515,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -555,170 +569,170 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -737,42 +751,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
